--- a/BANCO_ESPECIFICACOES.xlsx
+++ b/BANCO_ESPECIFICACOES.xlsx
@@ -1,425 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obras Civis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instalações Elétricas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instalações Hidrossanitárias" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados, Voz e CFTV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Climatização, Mecânica e Elevadores" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPCI - Prevenção e Combate a Incêndio" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Obras Civis" sheetId="1" r:id="rId1"/>
+    <sheet name="Instalações Elétricas" sheetId="2" r:id="rId2"/>
+    <sheet name="Dados, Voz e CFTV" sheetId="3" r:id="rId3"/>
+    <sheet name="Instalações Hidrossanitárias" sheetId="4" r:id="rId4"/>
+    <sheet name="Instalações Mecânicas" sheetId="5" r:id="rId5"/>
+    <sheet name="PPCI" sheetId="6" r:id="rId6"/>
+    <sheet name="Paisagismo" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E91"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -427,21 +24,13 @@
           <t>BANCO_ESPECIFICACOES - Obras Civis</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,3202 +62,2387 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>civil|001-faz-parte-do-servico-da-contratada-o-cro</t>
+          <t>civil|001-administracao-local-e-gestao-tecnica-da-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Faz parte do serviço da CONTRATADA: - O cronograma deverá estar baseado no cronograma físico-financeiro contratual</t>
+          <t>Administração Local e Gestão Técnica da Obra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; NR-35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>O cronograma deverá estar baseado no cronograma físico-financeiro contratual;</t>
+          <t>Compreende a gestão técnica e administrativa local da obra, incluindo manutenção de equipe técnica habilitada em campo, controle de qualidade, diário de obra, gestão documental, comunicação com o responsável pela fiscalização e cumprimento de obrigações contratuais e regulatórias. Não inclui a instalação física do canteiro, que é item próprio.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>civil|002-faz-parte-do-servico-da-contratada-o-cro</t>
+          <t>civil|002-placas-de-obra-e-identificacao-tecnica</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faz parte do serviço da CONTRATADA: - O cronograma deverá incluir: lista de entregas, atividades, predecessoras e suce</t>
+          <t>Placas de Obra e Identificação Técnica</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; Resolução CONFEA 198/1971</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>O cronograma deverá incluir: lista de entregas, atividades, predecessoras e sucessoras, durações previstas e respectivos custos;</t>
+          <t>Fornecimento e instalação de placa de obra com identificação da obra, responsável técnico e demais informações exigidas pela legislação e normas aplicáveis. As dimensões, quantidade e modelo devem atender à Resolução CONFEA 198/1971 e às exigências do órgão competente. A placa deve ser mantida em bom estado durante toda a execução da obra.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>civil|003-faz-parte-do-servico-da-contratada-a-ent</t>
+          <t>civil|003-locacao-topografica-nivelamento-e-gabari</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faz parte do serviço da CONTRATADA: - A entrega do cronograma deverá ser realizada após a assinatura do contrato, e su</t>
+          <t>Locação Topográfica, Nivelamento e Gabarito</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 6492; NR-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A entrega do cronograma deverá ser realizada após a assinatura do contrato, e sua aprovação pela FISCALIZAÇÃO será condição obrigatória para emissão da ordem de serviço e início das atividades em campo.</t>
+          <t>Locação planialtimétrica da obra com definição de alinhamentos, eixos, cotas de projeto, marcos topográficos e referências de nível (RN). Execução de gabaritos e controle de implantação durante toda a obra. Deve ser executado por profissional habilitado, com emissão de ART/RRT.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>civil|004-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|004-andaimes-tubulares-passarelas-e-platafor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Mobilização e execução das instalações da área ocupada pela CONTRATADA durante o</t>
+          <t>Andaimes Tubulares, Passarelas e Plataformas de Trabalho</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 6494; NR-11; NR-18; NR-35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mobilização e execução das instalações da área ocupada pela CONTRATADA durante os serviços – o canteiro de obras deverá ser montado dentro do espaço da obra, cabendo à CONTRATADA a organização do espaço para liberação e finalização dos serviços;</t>
+          <t>Fornecimento, montagem, manutenção e desmontagem de andaimes tubulares, passarelas e plataformas de trabalho para execução de serviços em altura, incluindo andaimes fachadeiros, suspensos e de interior conforme necessidade. Todos os sistemas devem atender às exigências da NR-18 e NR-35, com inspeção prévia, periódica e após eventos climáticos.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>civil|005-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|005-salas-provisorias-para-operacao-temporar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Limpeza, vigilância e proteção contra terceiros de todos os equipamentos, materi</t>
+          <t>Salas Provisórias para Operação Temporária Durante Obra</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 15758; NR-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Limpeza, vigilância e proteção contra terceiros de todos os equipamentos, materiais, ferramentas e demais elementos existentes no canteiro de obras;</t>
+          <t>Execução de ambientes provisórios para operação temporária durante a obra, utilizando sistema drywall com estrutura metálica, placas ST e pintura látex acrílica. Forro em painéis EPS quando aplicável. Os ambientes provisórios devem garantir condições mínimas de uso, segurança e isolamento acústico adequado à atividade. Desmontagem e recomposição das áreas ao final da obra são itens próprios.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>civil|006-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|006-mobilizacao-manutencao-e-desmobilizacao-</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Desmobilização</t>
+          <t>Mobilização, Manutenção e Desmobilização do Canteiro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; NR-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Desmobilização;</t>
+          <t>Instalação, manutenção durante toda a obra e desmobilização do canteiro, incluindo estruturas provisórias de escritório, laboratório, almoxarifado, vestiários, sanitários e demais instalações de apoio. O canteiro deve ser mantido em condições adequadas de funcionamento, higiene e segurança. Ao final da obra, todas as instalações provisórias devem ser removidas e a área entregue limpa.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>civil|007-observacao-geral-a-obra-devera-ser-fasea</t>
+          <t>civil|007-tapume-e-isolamento-fisico-de-obra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 - Serviços preliminares</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Observação geral: A obra deverá ser faseada em trechos, garantindo a operação da</t>
+          <t>Tapume e Isolamento Físico de Obra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; ABNT NBR 15575-1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Observação geral: A obra deverá ser faseada em trechos, garantindo a operação da Escola Sesi em ambientes provisórios durante a execução, priorizando a conclusão das salas de aula e das novas estruturas. Com a entrega destas, os espaços temporários serão desmobilizados para reforma. O cronograma faseado deverá ser discutido e validado junto à fiscalização da Firjan Sesi.</t>
+          <t>Fornecimento, montagem, manutenção e desmontagem de tapumes e barreiras físicas para isolamento da área de obra em relação a áreas de uso público ou em operação. O tapume deve garantir segurança de terceiros, impedir acesso não autorizado e, quando em vias públicas, atender às exigências da prefeitura local. Deve ser mantido em bom estado durante toda a obra.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>civil|008-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|008-protecao-de-elementos-e-estruturas-exist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 - Administração de obra</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Emissão de Laudo Técnico garantindo com ART (Anotação de Responsabilidade Técnic</t>
+          <t>Proteção de Elementos e Estruturas Existentes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emissão de Laudo Técnico garantindo com ART (Anotação de Responsabilidade Técnica) em atendimento a Nota Técnica NT 2-20 Controle de Materiais de Acabamento;</t>
+          <t>Proteção de elementos, estruturas, revestimentos, equipamentos e instalações existentes que devem ser preservados durante a execução da obra. Inclui o uso de mantas, telas, forros provisórios, bloqueios e demais dispositivos adequados ao risco de dano de cada elemento. Ao final dos serviços, as proteções devem ser removidas e os elementos inspecionados.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>civil|009-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|009-limpeza-vigilancia-e-guarda-de-materiais</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 - Administração de obra</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Elaboração do Plano de Emergência, que deverá estar mencionado na ART da obra</t>
+          <t>Limpeza, Vigilância e Guarda de Materiais no Canteiro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; CONAMA Resolução 307/2002</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elaboração do Plano de Emergência, que deverá estar mencionado na ART da obra.</t>
+          <t>Manutenção da limpeza do canteiro durante toda a obra, com retirada periódica de entulhos e resíduos. Guarda e proteção de materiais e equipamentos armazenados. Vigilância do canteiro para prevenção de furtos, vandalismo e acesso não autorizado, observando os requisitos de segurança aplicáveis.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>civil|010-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|010-guindastes-icamentos-e-levantamento-de-c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2 - Administração de obra</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relação dos principais serviços a serem executados: - Principais serviços gerais - Obtenção do Certificado de Aprovação e Certificado de Registro da piscina junto </t>
+          <t>Guindastes, Içamentos e Levantamento de Cargas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-11; NR-18; NR-35; ABNT NBR ISO 4306</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Obtenção do Certificado de Aprovação e Certificado de Registro da piscina junto ao CBMERJ, conforme Laudo de Exigências a ser fornecido pela CONTRATANTE;</t>
+          <t>Fornecimento, operação e manutenção de guindastes, gruas, manipuladores e demais equipamentos para içamento e movimentação de cargas pesadas no canteiro. Todas as operações devem ser realizadas por operadores habilitados, com inspeção prévia dos equipamentos e dispositivos de içamento. Plano de içamento deve ser elaborado para cargas críticas.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>civil|011-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|011-transporte-vertical-e-horizontal-de-mate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Serviços Preliminares</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fechamento com vidro das esquadrias após retirada do ar-condicionado de janela</t>
+          <t>Transporte Vertical e Horizontal de Materiais, Equipamentos e Resíduos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-11; NR-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fechamento com vidro das esquadrias após retirada do ar-condicionado de janela;</t>
+          <t>Transporte interno de materiais, equipamentos e resíduos dentro do canteiro, tanto na horizontal (entre frentes de trabalho) quanto na vertical (entre pavimentos), utilizando elevadores de carga, cremalheiras, carrinhos ou outros meios adequados. O transporte deve garantir a integridade dos materiais e a segurança dos trabalhadores.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>civil|012-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|012-divisorias-provisorias-em-drywall-st</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Apresentação de plano da utilização de resíduos sólidos oriundos de demolição lo</t>
+          <t>Divisórias Provisórias em Drywall ST</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15758; ABNT NBR 14715; NR-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Apresentação de plano da utilização de resíduos sólidos oriundos de demolição local no próprio terreno da obra e utilização de material terroso (quando não contaminado), no próprio terreno da obra;</t>
+          <t>Execução de divisórias provisórias em sistema drywall com perfis metálicos e chapas de gesso ST, para delimitação de ambientes durante obras em edificações em uso. As divisórias devem garantir isolamento adequado entre a área de obra e as áreas operacionais, com acabamento mínimo compatível com o uso do espaço adjacente.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>civil|013-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|013-reforcos-em-drywall-para-vaos-portas-e-p</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Remoção do entulho gerado</t>
+          <t>Reforços em Drywall para Vãos, Portas e Passagem de Instalações</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15758; NR-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Remoção do entulho gerado;</t>
+          <t>Execução de reforços estruturais em paredes de drywall provisórias para atender a vãos de portas, passagens de instalações elétricas, hidráulicas e demais interferências. Os reforços devem ser dimensionados conforme os carregamentos e esforços previstos, utilizando perfis metálicos reforçados ou elementos de compensado em pontos específicos.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>civil|014-demolicoes-areas-externas-demolicao-da-g</t>
+          <t>civil|014-reaproveitamento-reinstalacao-e-ajuste-d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição da guarita existente</t>
+          <t>Reaproveitamento, Reinstalação e Ajuste de Portas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Demolição da guarita existente.</t>
+          <t>Retirada cuidadosa, armazenamento, ajuste e reinstalação de portas existentes reaproveitadas em divisórias ou ambientes provisórios. Inclui eventuais ajustes de folha, ferragens e batentes para adequação ao novo vão. As portas reaproveitadas devem estar em bom estado e garantir funcionalidade e segurança.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>civil|015-demolicoes-areas-externas-demolicao-subs</t>
+          <t>civil|015-forro-provisorio-em-painel-eps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição/substituição da pavimentação completa do estacionamento (piso em cimen</t>
+          <t>Forro Provisório em Painel EPS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Demolição/substituição da pavimentação completa do estacionamento (piso em cimentado e intertravado).</t>
+          <t>Fornecimento e instalação de forro provisório em painéis de EPS (poliestireno expandido) fixados em estrutura metálica leve ou pendural. O forro deve garantir isolamento mínimo necessário para as atividades realizadas no espaço provisório. Desmontagem ao final da necessidade de uso.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>civil|016-demolicoes-areas-externas-retirada-dos-p</t>
+          <t>civil|016-desmontagem-de-instalacoes-provisorias-e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Retirada dos portões de pedestres e veículos motorizados para substituição</t>
+          <t>Desmontagem de Instalações Provisórias e Recomposição de Áreas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; CONAMA Resolução 307/2002</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Retirada dos portões de pedestres e veículos motorizados para substituição.</t>
+          <t>Desmontagem de todas as instalações provisórias civis ao final da necessidade de uso, incluindo divisórias, forros, tapumes internos, proteções e demais elementos temporários. As áreas afetadas devem ser recompostas ao estado original ou ao estado previsto em projeto, com reparos em pisos, paredes, tetos e qualquer elemento danificado durante a montagem ou operação das instalações provisórias.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>civil|017-demolicoes-areas-externas-demolicao-de-t</t>
+          <t>civil|017-limpeza-preparo-do-terreno-e-remocao-ini</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição de trechos entre pilares do muro de divisa</t>
+          <t>Limpeza, Preparo do Terreno e Remoção Inicial de Interferências</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>CONAMA Resolução 307/2002; Lei Federal 12.305/2010; ABNT NBR 10004; NR-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Demolição de trechos entre pilares do muro de divisa.</t>
+          <t>Remoção de vegetação, entulhos, resíduos, raízes, elementos construtivos e demais interferências existentes na área de intervenção. O material removido deverá ser destinado conforme legislação ambiental vigente, incluindo CONAMA 307/2002 para resíduos de construção civil.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>civil|018-demolicoes-areas-externas-demolicao-de-t</t>
+          <t>civil|018-escavacao-manual-e-mecanizada-para-funda</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição de trecho da quadra de areia do Sesi</t>
+          <t>Escavação Manual e Mecanizada para Fundações e Valas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 6122; NR-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Demolição de trecho da quadra de areia do Sesi.</t>
+          <t>Escavação manual ou mecanizada para implantação de fundações, blocos, cintas e valas que requeiram rebaixamento do terreno. Devem ser respeitados os taludes de segurança conforme tipo de solo e profundidade. Escoramento e rebaixamento do lençol freático são itens próprios quando necessários.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>civil|019-demolicoes-areas-externas-demolicao-meca</t>
+          <t>civil|019-reaterro-e-aterro-compactado-com-materia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição mecanizada das paredes dos terraços no térreo para construção das nova</t>
+          <t>Reaterro e Aterro Compactado com Material Selecionado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 6457; NBR 7182; NR-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Demolição mecanizada das paredes dos terraços no térreo para construção das novas salas de aula.</t>
+          <t>Reaterro de valas e execução de aterros compactados mecanicamente em camadas de no máximo 20 cm, com controle de umidade e grau de compactação mínimo de 95% do Proctor Normal conforme projeto. O material de aterro deve ser selecionado, isento de matéria orgânica, torrões e pedras de dimensão incompatível. Ensaios de controle devem ser realizados conforme frequência definida em projeto.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>civil|020-demolicoes-areas-externas-demolicao-de-m</t>
+          <t>civil|020-escoramento-e-esgotamento-de-cavas-e-val</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição de muros de divisa dos terraços (conforme projeto)</t>
+          <t>Escoramento e Esgotamento de Cavas e Valas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 6122; NR-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Demolição de muros de divisa dos terraços (conforme projeto).</t>
+          <t>Execução de escoramento de paredes de cavas e valas em profundidades que requeiram contenção, conforme tipo de solo e análise geotécnica. Esgotamento contínuo quando houver presença de água, com uso de bombas de rebaixamento do lençol freático. O sistema de escoramento deve ser dimensionado por profissional habilitado para profundidades superiores a 1,25 m.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>civil|021-demolicoes-areas-externas-demolicao-de-r</t>
+          <t>civil|021-escavacao-de-valas-para-instalacoes-ente</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição de revestimentos de pisos (cerâmica, porcelanato, manta vinílica), par</t>
+          <t>Escavação de Valas para Instalações Enterradas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NR-18; NBR 7370</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Demolição de revestimentos de pisos (cerâmica, porcelanato, manta vinílica), paredes e teto em rebaixo para instalação de novos revestimentos.</t>
+          <t>Escavação de valas para implantação de redes de instalações enterradas (hidráulicas, sanitárias, elétricas, drenagem e outras), com larguras e profundidades conforme projetos de cada disciplina. Inclui regularização do fundo da vala e preparo do leito de assentamento quando aplicável.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>civil|022-demolicoes-areas-externas-demolicao-de-e</t>
+          <t>civil|022-remocao-carga-e-transporte-de-material-e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Demolição de eletrocalhas, perfilados e esquadrias, conforme projeto</t>
+          <t>Remoção, Carga e Transporte de Material Excedente</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>CONAMA Resolução 307/2002; Lei Federal 12.305/2010; ABNT NBR 10004; NR-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Demolição de eletrocalhas, perfilados e esquadrias, conforme projeto.</t>
+          <t>Remoção, carga e transporte de material excedente proveniente de escavações, demolições e limpeza, com destinação em local licenciado conforme legislação ambiental vigente. O transporte deve ser realizado por veículos adequados e com controle de emissão de particulados.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>civil|023-demolicoes-areas-externas-retirada-de-po</t>
+          <t>civil|023-regularizacao-e-compactacao-de-plataform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Movimento de Terra</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Retirada de portas, divisórias, bancadas e equipamentos hidráulicos, com reaprov</t>
+          <t>Regularização e Compactação de Plataformas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>NBR 7182; NBR 6457; NR-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Retirada de portas, divisórias, bancadas e equipamentos hidráulicos, com reaproveitamento e guarda para uso.</t>
+          <t>Regularização e compactação mecanizada de plataformas de trabalho, áreas de estacionamento, pátios e substratos para pavimentação. Deve ser atingido o grau de compactação mínimo previsto em projeto, verificado por ensaios de densidade in situ.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>civil|024-demolicoes-areas-externas-retirada-de-tr</t>
+          <t>civil|024-execucao-de-estrutura-de-concreto-armado</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Estrutura</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Retirada de traves e tabelas do ginásio</t>
+          <t>Execução de Estrutura de Concreto Armado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 12655; ABNT NBR 5738; ABNT NBR 5739; ABNT NBR 6118</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Retirada de traves e tabelas do ginásio.</t>
+          <t>Execução de estrutura de concreto armado (sapatas, pilares, vigas, lajes) com concreto usinado fck = 30 MPa, slump 10 ± 2 cm. Cimbramento e escoramentos devem permanecer pelo tempo necessário à cura conforme projeto.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>civil|025-demolicoes-areas-externas-remocao-de-arv</t>
+          <t>civil|025-montagem-de-estrutura-metalica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Estrutura</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Remoção de árvores e vegetação em áreas de obra</t>
+          <t>Montagem de Estrutura Metálica</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14323; ABNT NBR 14432; ABNT NBR 8800; AWS D1.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Remoção de árvores e vegetação em áreas de obra.</t>
+          <t>Fornecimento, fabricação e montagem de estrutura metálica em perfis W, soldas AWS E70XX. Tratamento com primer epoxídico 75 μm e esmalte epóxi 100 μm. Partes com risco de fogo recebem intumescente Renitherm PMA 600 ou similar de equivalência técnica conforme TRRF (NBR 14432).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>civil|026-demolicoes-pavimento-terreo-escola-demol</t>
+          <t>civil|026-impermeabilizacao-com-manta-asfaltica-4-</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Impermeabilizações</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Demolição de todos os pisos da área da escola (exceto academia e quadra)</t>
+          <t>Impermeabilização com Manta Asfáltica 4 mm – Novas Lajes de Cobertura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9574; ABNT NBR 9575; ABNT NBR 9952</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Demolição de todos os pisos da área da escola (exceto academia e quadra).</t>
+          <t>Impermeabilização de novas lajes de cobertura com manta asfáltica 4 mm, aplicada a maçarico, sobre primer asfáltico. Viradas em todas as vigas e muretas, subidas de 40 cm em paredes.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>civil|027-demolicoes-pavimento-terreo-escola-demol</t>
+          <t>civil|027-impermeabilizacao-de-sanitarios-com-arga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Impermeabilizações</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Demolição de alvenarias e divisórias para adequações de layout</t>
+          <t>Impermeabilização de Sanitários com Argamassa Polimérica</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9574; ABNT NBR 9575</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Demolição de alvenarias e divisórias para adequações de layout.</t>
+          <t>Impermeabilização de pisos e paredes de sanitários com argamassa polimérica bicomponente em no mínimo 2 demãos cruzadas, reforço em tela de poliéster. Teste lâmina d'água por no mínimo 72 horas.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>civil|028-demolicoes-pavimento-terreo-escola-demol</t>
+          <t>civil|028-impermeabilizante-acrilico-tecryl-d3-are</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Impermeabilizações</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Demolição de esquadrias conforme projeto</t>
+          <t>Impermeabilizante Acrílico Tecryl D3 – Área de Condensadoras na Cobertura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9574; ABNT NBR 9575</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Demolição de esquadrias conforme projeto.</t>
+          <t>Aplicação de impermeabilizante flexível de base acrílica Tecryl D3 ou similar de equivalência técnica na área das condensadoras na cobertura. Mínimo 2 demãos cruzadas, sobre superfície limpa e seca.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>civil|029-demolicoes-pavimento-terreo-escola-demol</t>
+          <t>civil|029-revestimento-de-impermeabilizacao-em-fun</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Impermeabilizações</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Demolição de revestimentos cerâmicos em sanitários sem alteração de layout</t>
+          <t>Revestimento de Impermeabilização em Fundações</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9574; ABNT NBR 9575</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Demolição de revestimentos cerâmicos em sanitários sem alteração de layout.</t>
+          <t>Impermeabilização das faces externas de fundações em contato com o solo. Executada após cura do concreto e antes do reaterro. Argamassa 1:3 com aditivo impermeabilizante Vedacit ou similar de equivalência técnica.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>civil|030-demolicoes-pavimento-terreo-escola-louca</t>
+          <t>civil|030-teste-de-lamina-d-agua-72-horas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Impermeabilizações</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Louças, metais, acessórios e bancadas dos sanitários (remoção)</t>
+          <t>Teste de Lâmina d'Água – 72 horas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9574; ABNT NBR 9575</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Louças, metais, acessórios e bancadas dos sanitários (remoção).</t>
+          <t>Após qualquer sistema de impermeabilização, realizar teste de lâmina d'água por no mínimo 72 horas. Acompanhado e aprovado pela Fiscalização antes do prosseguimento dos serviços.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>civil|031-demolicoes-1o-pavimento-escola-e-saude-d</t>
+          <t>civil|031-telhamento-com-telha-de-aco-aluminio-e-0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Telhados e Coberturas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Demolições - 1º pavimento – Escola e Saúde - Demolição de todos os pisos existentes</t>
+          <t>Telhamento com Telha de Aço/Alumínio e=0,5 mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14513</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Demolição de todos os pisos existentes.</t>
+          <t>Fornecimento e instalação de telhas de aço ou alumínio e=0,5 mm, termolacadas, perfil conforme projeto. Vedação com rufos e arremates metálicos.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>civil|032-demolicoes-1o-pavimento-escola-e-saude-d</t>
+          <t>civil|032-instalacao-de-calhas-e-rufos-em-galvalum</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Telhados e Coberturas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Demolições - 1º pavimento – Escola e Saúde - Demolição de divisórias, alvenarias e esquadrias conforme projeto</t>
+          <t>Instalação de Calhas e Rufos em Galvalume</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 10844</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Demolição de divisórias, alvenarias e esquadrias conforme projeto.</t>
+          <t>Calhas em galvalume chapa 0,7 mm, desenvolvimento 0,50 m. Rufos em galvalume. Caimentos mínimos de 0,5%. Conforme ABNT NBR 10844.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>civil|033-demolicoes-1o-pavimento-escola-e-saude-d</t>
+          <t>civil|033-execucao-de-alvenaria-de-bloco-ceramico-</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Alvenarias e Vedações</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Demolições - 1º pavimento – Escola e Saúde - Demolição de guarda-corpo em ferro e vidro na varanda</t>
+          <t>Execução de Alvenaria de Bloco Cerâmico e Bloco de Concreto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15270; ABNT NBR 15961; ABNT NBR 6136</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Demolição de guarda-corpo em ferro e vidro na varanda.</t>
+          <t>Alvenaria de vedação e estrutural em blocos cerâmicos ou de concreto. Vergas e contravergas em concreto armado em todos os vãos.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>civil|034-servicos-externos-demolicao-de-trecho-da</t>
+          <t>civil|034-execucao-de-parede-em-placa-cimenticia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Alvenarias e Vedações</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serviços externos - Demolição de trecho da calçada, com construção de enchimento, base de concreto m</t>
+          <t>Execução de Parede em Placa Cimentícia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15498; ABNT NBR 15758</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Demolição de trecho da calçada, com construção de enchimento, base de concreto magro, base para assentamento e piso intertravado nivelado com as soleiras da quadra e dos acessos às circulações da escola, conforme indicado em projeto.</t>
+          <t>Vedação em placa cimentícia sobre estrutura metálica galvanizada. Juntas seladas com fita e massa. Tratamento hidrofugante nas faces externas.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>civil|035-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|035-execucao-de-paredes-em-drywall</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Alvenarias e Vedações</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Demolição de divisórias e alvenarias conforme projeto</t>
+          <t>Execução de Paredes em Drywall</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14715; ABNT NBR 15758</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Demolição de divisórias e alvenarias conforme projeto;</t>
+          <t>Paredes em drywall com perfis galvanizados e chapas ST, RU ou RF conforme projeto. Tratamento de juntas com fita e massa. Lã mineral para isolamento termoacústico.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>civil|036-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|036-chapisco-em-alvenarias-e-estruturas-de-c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Demolição de muros de divisa dos terraços</t>
+          <t>Chapisco em Alvenarias e Estruturas de Concreto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13749; ABNT NBR 7200</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Demolição de muros de divisa dos terraços;</t>
+          <t>Chapisco com argamassa de cimento e areia traço 1:3, espessura ~5 mm, sobre alvenarias e concreto previamente limpos e umedecidos.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>civil|037-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|037-execucao-de-emboco</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Retirada das árvores nas áreas de construção</t>
+          <t>Execução de Emboço</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13749; ABNT NBR 7200</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Retirada das árvores nas áreas de construção;</t>
+          <t>Emboço com argamassa de cimento e areia, taliscas de nivelamento, espessura média 1,5 cm. Sarrafeado, desempenado e curado por no mínimo 3 dias.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>civil|038-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|038-assentamento-de-porcelanato-em-paredes-e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Demolição de árvores conforme projeto</t>
+          <t>Assentamento de Porcelanato em Paredes – Eliane Forma Slim / Munari Marfim</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13528; ABNT NBR 13754; ABNT NBR 14081</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Demolição de árvores conforme projeto;</t>
+          <t>Eliane Forma Slim 30×60 cm ou similar de equivalência técnica para sanitários e Munari Marfim 60×60 cm ou similar de equivalência técnica para demais ambientes. ACIII, rejunte epóxi ou cimentício. Juntas de movimentação a cada 4 m.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>civil|039-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|039-revestimento-de-parede-em-mdf-laminado</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Demolição de divisórias, alvenarias e esquadrias conforme projeto</t>
+          <t>Revestimento de Parede em MDF Laminado</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15316</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Demolição de divisórias, alvenarias e esquadrias conforme projeto;</t>
+          <t>Painéis de MDF com laminado melamínico, HPL ou pintura, fixados sobre estrutura de madeira ou perfis metálicos. Juntas com perfis de alumínio ou ABS.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>civil|040-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|040-brise-metalico-em-aluminio-anodizado-1-2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Revestimentos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Demolição de guarda-corpo de ferro e vidro, na varanda</t>
+          <t>Brise Metálico em Alumínio Anodizado 1,2 mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 10908</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Demolição de guarda-corpo de ferro e vidro, na varanda.</t>
+          <t>Brise metálico em alumínio anodizado 1,2 mm, fixado em cantoneiras de aço conforme projeto. Parafusos inox. Silicone neutro nas juntas.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>civil|041-servicos-do-1-pavimento-area-de-saude-de</t>
+          <t>civil|041-execucao-de-contrapiso-em-argamassa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3 - Demolições e retiradas</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Demolição de guarda-corpo de ferro e vidro na varanda e construção de novas esqu</t>
+          <t>Execução de Contrapiso em Argamassa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 7200</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Demolição de guarda-corpo de ferro e vidro na varanda e construção de novas esquadrias.</t>
+          <t>Contrapiso em argamassa de cimento e areia, espessura 15–25 mm, sarrafeado e desempenado. Caimentos para ralos respeitados.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>civil|042-demolicoes-areas-externas-movimentacao-d</t>
+          <t>civil|042-piso-vinilico-pvc-3-mm-classe-32-madeira</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4 - Movimento de terra</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Movimentação de terra para:</t>
+          <t>Piso Vinílico PVC 3 mm Classe 32 – Madeirado Paglia / Aveia</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16192; EN 649</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Movimentação de terra para:.</t>
+          <t>Piso vinílico PVC em placas 152×914 mm, classe 32, e=3 mm. Colado sobre contrapiso regularizado. Rodapé em PVC vinílico do mesmo fabricante.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>civil|043-demolicoes-areas-externas-construcao-de-</t>
+          <t>civil|043-piso-em-porcelanato-eliane-munari-marfim</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4 - Movimento de terra</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Demolições - Áreas externas - Construção de novas salas de aula na área dos terraços</t>
+          <t>Piso em Porcelanato Eliane Munari Marfim 60×60 cm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13816; ABNT NBR 14081</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Construção de novas salas de aula na área dos terraços.</t>
+          <t>Porcelanato Eliane Munari Marfim 60×60 cm ou similar de equivalência técnica, ACIII, rejunte epóxi. Juntas de movimentação a cada 4 m.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>civil|044-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|044-piso-monolitico-para-playground-80-mm-au</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6 - Estrutura Metálica</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução de novas construções com fundações e cintas de concreto, pilares e viga</t>
+          <t>Piso Monolítico para Playground 80 mm – Aubicon ou similar de equivalência técnica</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16071; EN 1177</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Execução de novas construções com fundações e cintas de concreto, pilares e vigas metálicos e de concreto e lajes de concreto armado e steel deck, conforme projetos específicos de estrutura anexos;</t>
+          <t>Piso monolítico em borracha reciclada para playground, e=80 mm, colorido conforme projeto. Sistema contínuo sobre base de concreto nivelada.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>civil|045-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|045-piso-intertravado-16-faces-para-pedestre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6 - Estrutura Metálica</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Instalação de corrimãos e guarda-corpos, conforme projeto e especificações</t>
+          <t>Piso Intertravado 16 Faces para Pedestres 27×9×8 cm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9781</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Instalação de corrimãos e guarda-corpos, conforme projeto e especificações;</t>
+          <t>Piso intertravado onda 16 faces 27×9×8 cm para pedestres. Leito de areia 3–5 cm. fck ≥ 35 MPa. Juntas 2 mm.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>civil|046-servicos-externos-construcao-de-nova-esc</t>
+          <t>civil|046-piso-intertravado-16-faces-para-veiculos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6 - Estrutura Metálica</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serviços externos - Construção de nova escada metálica e patamar para acesso ao 1° pavimento</t>
+          <t>Piso Intertravado 16 Faces para Veículos 27×9×8 cm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9781</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Construção de nova escada metálica e patamar para acesso ao 1° pavimento;</t>
+          <t>Piso intertravado onda 16 faces 27×9×8 cm para veículos, fck ≥ 35 MPa. Base granular compactada. Leito de areia 3–5 cm.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>civil|047-servicos-do-pavimento-terreo-quadra-poli</t>
+          <t>civil|047-execucao-de-piso-cimentado</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6 - Estrutura Metálica</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Construção de alvenaria de bloco cerâmico na horizontal colada na parede de divi</t>
+          <t>Execução de Piso Cimentado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 7583</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Construção de alvenaria de bloco cerâmico na horizontal colada na parede de divisa com a nova escada;</t>
+          <t>Piso cimentado traço 1:3, acabamento liso, e=3 cm. Juntas serradas 5 mm × 4 cm. Tarugo de polietileno e selante de silicone.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>civil|048-servicos-do-1-pavimento-mezanino-quadra-</t>
+          <t>civil|048-grade-de-piso-em-malha-de-aco-eletrofund</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6 - Estrutura Metálica</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Mezanino quadra poliesportiva - Construção de depósito em alambrado</t>
+          <t>Grade de Piso em Malha de Aço Eletrofundida Galvanizada</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 7008; ASTM A-123</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Construção de depósito em alambrado;</t>
+          <t>Grade de piso eletrofundida galvanizada a quente ASTM A-123, superfície S1. Grampos de fixação em inox.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>civil|049-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|049-piso-modular-indoor-em-polipropileno-250</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8 - Telhados e coberturas</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução das impermeabilizações, platibandas, com instalação das calhas, chapins</t>
+          <t>Piso Modular Indoor em Polipropileno 250×250×12 mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15887</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Execução das impermeabilizações, platibandas, com instalação das calhas, chapins, rufos e demais acessórios conforme projeto;</t>
+          <t>Piso modular para quadras esportivas em PP, placas 250×250×12 mm, antiderrapante, com manta de absorção de impacto PEBD 3 mm. Demarcações em filme vinílico ≥0,20 mm.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>civil|050-demolicoes-cobertura-pavimento-tecnico-s</t>
+          <t>civil|050-assentamento-de-meio-fio-de-concreto-pre</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8 - Telhados e coberturas</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Demolições - Cobertura / Pavimento técnico - Sem demolições</t>
+          <t>Assentamento de Meio-Fio de Concreto Pré-Fabricado</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 11376</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sem demolições.</t>
+          <t>Meio-fio de concreto pré-fabricado 100×15×13×20 cm sobre concreto magro. Juntas com argamassa.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>civil|051-servicos-externos-construcao-de-cobertur</t>
+          <t>civil|051-piso-em-granito-cinza-andorinha-polido-2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8 - Telhados e coberturas</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serviços externos - Construção de cobertura de abrigo para as catracas do acesso do Sesi Lazer</t>
+          <t>Piso em Granito Cinza Andorinha Polido 2 cm – Elevador</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14081; ABNT NBR 15844</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Construção de cobertura de abrigo para as catracas do acesso do Sesi Lazer;</t>
+          <t>Granito Cinza Andorinha polido e=2 cm. Argamassa 1:3 ou colante para pedras. Juntas 1–3 mm com rejunte epóxi.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>civil|052-servicos-do-1-pavimento-servicos-das-laj</t>
+          <t>civil|052-piso-tatil-de-alerta-e-direcional-em-pvc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8 - Telhados e coberturas</t>
+          <t>Pisos e Pavimentações</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Serviços das lajes de cobertura – pavimentos técnicos - Construção de alvenarias em blocos cerâmicos de suporte para quadros e leitos de</t>
+          <t>Piso Tátil de Alerta e Direcional em PVC ou Cerâmico</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16537; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Construção de alvenarias em blocos cerâmicos de suporte para quadros e leitos de instalações;</t>
+          <t>Piso tátil alerta e direcional, cor amarela, 25×25 cm, ACIII. Atende ABNT NBR 9050:2020 e NBR 16537.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>civil|053-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|053-fornecimento-e-instalacao-de-esquadrias-</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9 - Alvenarias e vedações</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução de alvenarias e divisórias, com seus respectivos acabamentos conforme p</t>
+          <t>Fornecimento e Instalação de Esquadrias de Madeira</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 11711; ABNT NBR 8542; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Execução de alvenarias e divisórias, com seus respectivos acabamentos conforme projetos e especificações;</t>
+          <t>Madeira de reflorestamento certificada. Ferragens La Fonte Architect Inox CJ892 ou similar de equivalência técnica. Largura mínima 80 cm para acessibilidade. Fixação com espuma expansiva.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>civil|054-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|054-fornecimento-e-instalacao-de-esquadrias-</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9 - Alvenarias e vedações</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de novas salas com divisórias de gesso acartonado duplo e chapa cimen</t>
+          <t>Fornecimento e Instalação de Esquadrias de Alumínio</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 10908; ABNT NBR 11706; ABNT NBR 7199</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Construção de novas salas com divisórias de gesso acartonado duplo e chapa cimentícia;</t>
+          <t>Alumínio anodizado natural ou eletrostático branco. Vidro temperado 10 mm. Vedações EPDM. Silicone estrutural e neutro.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>civil|055-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|055-pelicula-3m-fasara-milky-white-controle-</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9 - Alvenarias e vedações</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de elemento vazado na parede do corredor dos vestiários</t>
+          <t>Película 3M Fasara Milky White – Controle Solar</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 7199</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Instalação de elemento vazado na parede do corredor dos vestiários;</t>
+          <t>Película 3M Fasara Milky White ou similar de equivalência técnica nos vidros indicados. Aplicação por instalador habilitado. Sem bolhas ou descamações.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>civil|056-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|056-porta-corta-fogo-pcf3-p90-1-802-10-m</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9 - Alvenarias e vedações</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Construção de novas salas com divisórias de gesso acartonado duplo e/ou placa ci</t>
+          <t>Porta Corta-Fogo PCF3 P90 – 1,80×2,10 m</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 11742; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Construção de novas salas com divisórias de gesso acartonado duplo e/ou placa cimentícia;</t>
+          <t>Porta corta-fogo em chapa de aço, PCF3 (P-90), 1,80×2,10 m, marco metálico, mola de fechamento automático e barra antipânico. Certificada INMETRO.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>civil|057-servicos-do-1-pavimento-area-de-saude-co</t>
+          <t>civil|057-gc01-em-aluminio-e-corrimaos-gc02-gc03-e</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9 - Alvenarias e vedações</t>
+          <t>Esquadrias</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Construção de novas salas com divisórias de gesso acartonado duplo</t>
+          <t>GC01 em Alumínio e Corrimãos GC02/GC03 em Aço Galvanizado</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14718; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Construção de novas salas com divisórias de gesso acartonado duplo;</t>
+          <t>GC01: tubos de alumínio 40×40 mm, h=0,90 m, eletrostático branco. GC02/GC03: aço galvanizado Ø 1½", dupla altura, NBR 9050:2020.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>civil|058-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|058-forro-em-gesso-acartonado-st-12-5-mm-pin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Forros e Divisórias</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Toda movimentação de terra, escavações, reaterro e descarte necessário para a ob</t>
+          <t>Forro em Gesso Acartonado ST 12,5 mm – Pintura Branca</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 12127; ABNT NBR 14715</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Toda movimentação de terra, escavações, reaterro e descarte necessário para a obra, toda a pavimentação e infra-estrutura da área de intervenção;</t>
+          <t>Chapas ST 12,5 mm sobre estrutura galvanizada e tirantes. Tratamento de juntas. Pintura PVA ou acrílica branco.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>civil|059-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|059-forro-modulado-thermatex-star-625625-mm-</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Forros e Divisórias</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Regularização de contrapiso existente e execução nos novos contrapisos</t>
+          <t>Forro Modulado THERMATEX Star 625×625 mm – Knauff ou similar de equivalência técnica</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 11678</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Regularização de contrapiso existente e execução nos novos contrapisos;</t>
+          <t>Forro modulado em fibra mineral 625×625 mm, THERMATEX Star Knauff ou similar de equivalência técnica, em estrutura de perfis T galvanizado. Cor branco.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>civil|060-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|060-forro-modulado-antibacteriano-lavavel-62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Forros e Divisórias</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução de pisos e pavimentações conforme projetos e especificações, com especi</t>
+          <t>Forro Modulado Antibacteriano Lavável 625×625 mm – Armstrong Scala Square ou similar de equivalência técnica</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14715; RDC ANVISA 50/2002</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Execução de pisos e pavimentações conforme projetos e especificações, com especial atenção aos trechos de pavimentação que serão refeitos e/ou recompostos na edificação existente, conforme descrito em item específico;</t>
+          <t>Forro modulado em fibra mineral antibacteriano (lavável) 625×625 mm Armstrong Scala Square ou similar de equivalência técnica para áreas de saúde.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>civil|061-demolicoes-pavimento-terreo-escola-execu</t>
+          <t>civil|061-rodapes-em-poliestireno-porcelanato-e-co</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Rodapés, Soleiras e Bancadas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Execução de contrapiso novo ou regularização do existente</t>
+          <t>Rodapés em Poliestireno, Porcelanato e Concreto</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14081</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Execução de contrapiso novo ou regularização do existente.</t>
+          <t>Rodapé Santa Luzia ou similar de equivalência técnica poliestireno h=5 cm branco e h=3 cm preto. Rodapé porcelanato Eliane ou similar de equivalência técnica nos sanitários. Rodapé concreto pré-moldado 7×100×2 cm externo.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>civil|062-servicos-externos-substituicao-do-calcam</t>
+          <t>civil|062-soleiras-chapins-peitoris-e-bancadas-em-</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Rodapés, Soleiras e Bancadas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços externos - Substituição do calçamento dos acessos à escola e ao Sesi Lazer e instalação de </t>
+          <t>Soleiras, Chapins, Peitoris e Bancadas em Granito Branco Ceará Polido</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15844</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Substituição do calçamento dos acessos à escola e ao Sesi Lazer e instalação de pisos táteis;</t>
+          <t>Granito Branco Ceará polido e=2 cm. Argamassa 1:3 ou colante. Pingadeira lateral ≥1,5 cm em bancadas.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>civil|063-servicos-externos-substituicao-de-toda-p</t>
+          <t>civil|063-cuba-de-louca-deca-l-37-lavatorio-branco</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serviços externos - Substituição de toda pavimentação das pistas de veículos nos estacionamentos com</t>
+          <t>Cuba de Louça Deca L.37 – Lavatório Branco</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Substituição de toda pavimentação das pistas de veículos nos estacionamentos com piso intertravado;</t>
+          <t>Cuba de louça Deca L.37 ou similar de equivalência técnica branco. Válvula de escoamento metal cromado e sifão flexível PVC.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>civil|064-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|064-lavatorio-suspenso-pcd-deca-vogue-plus-l</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Substituição do piso existente por piso de porcelanato, piso vinílico e instalaç</t>
+          <t>Lavatório Suspenso PCD – Deca Vogue Plus L.51 / L.510.17</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Substituição do piso existente por piso de porcelanato, piso vinílico e instalação de pisos táteis;</t>
+          <t>Lavatório suspenso PCD Deca Vogue Plus L.51 ou similar de equivalência técnica, branco. Altura e afastamentos conforme NBR 9050:2020. Torneira de fechamento automático com alavanca para PCD.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>civil|065-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|065-cuba-de-aco-inoxidavel-aisi-304-50040020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de piso emborrachado no pátio interno</t>
+          <t>Cuba de Aço Inoxidável AISI 304 – 500×400×200 mm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Instalação de piso emborrachado no pátio interno;</t>
+          <t>Cuba inox AISI 304, chapa #20, 500×400×200 mm. Válvula Ø 1.1/2" e sifão Ø 1.1/2"×3.3/4".</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>civil|066-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|066-vaso-sanitario-convencional-deca-ravena-</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Substituição do piso por novo em porcelanato</t>
+          <t>Vaso Sanitário Convencional – Deca Ravena P.9 Branco</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Substituição do piso por novo em porcelanato;</t>
+          <t>Vaso Deca Ravena P.9 ou similar de equivalência técnica branco, assento plástico, anel de vedação, canopla e tubo de ligação cromados. Engate flexível inox 1/2"×40 cm.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>civil|067-servicos-do-pavimento-terreo-quadra-poli</t>
+          <t>civil|067-vaso-sanitario-pcd-deca-vogue-plus-p-510</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Repintura das paredes e do piso, com recomposição completa do piso</t>
+          <t>Vaso Sanitário PCD – Deca Vogue Plus P.510 Branco</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Repintura das paredes e do piso, com recomposição completa do piso;</t>
+          <t>Vaso Deca Vogue Plus P.510 ou similar de equivalência técnica branco para PCD. Altura e afastamentos conforme NBR 9050:2020.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>civil|068-servicos-do-pavimento-terreo-quadra-poli</t>
+          <t>civil|068-mictorio-deca-m-714-decamatic-eco-2574-c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Construção de degraus intermediários na arquibancada</t>
+          <t>Mictório Deca M.714 Decamatic Eco 2574.C – Anti-Vandalismo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Construção de degraus intermediários na arquibancada;</t>
+          <t>Mictório Deca M.714 ou similar de equivalência técnica com válvula Decamatic Eco 2574.C ou similar de equivalência técnica embutida anti-vandalismo.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>civil|069-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|069-bacia-sanitaria-infantil-celite-linha-ki</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Substituição do piso existente por piso de porcelanato</t>
+          <t>Bacia Sanitária Infantil – Celite Linha Kids</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097; ABNT NBR 5688</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Substituição do piso existente por piso de porcelanato;</t>
+          <t>Bacia sanitária infantil louça branca Celite Kids ou similar de equivalência técnica. Assento infantil, anel de vedação.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>civil|070-servicos-do-1-pavimento-area-de-saude-su</t>
+          <t>civil|070-torneira-de-fechamento-automatico-fabrim</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11 - Pisos e Pavimentações</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Substituição do piso existente por piso de porcelanato nos novos ambientes</t>
+          <t>Torneira de Fechamento Automático – Fabrimar Acquapress Anti-Vandalismo</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Substituição do piso existente por piso de porcelanato nos novos ambientes;</t>
+          <t>Torneira automática para lavatório, acabamento cromado, arejador anti-vandalismo, Fabrimar Acquapress ou similar de equivalência técnica.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>civil|071-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|071-torneira-bica-alta-para-cozinha-deca-lin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Instalação de esquadrias de madeira, alumínio e vidro</t>
+          <t>Torneira Bica Alta para Cozinha – Deca Link 1167.C.LNK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Instalação de esquadrias de madeira, alumínio e vidro;</t>
+          <t>Torneira de mesa para cozinha tipo bica alta com bico articulado e arejador embutido. Deca Link 1167.C.LNK ou similar de equivalência técnica, acabamento cromado.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>civil|072-servicos-externos-construcao-de-mureta-e</t>
+          <t>civil|072-chuveiro-de-emergencia-com-lava-olhos-cl</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços externos - Construção de mureta em bloco de concreto estrutural com espaços para comportas </t>
+          <t>Chuveiro de Emergência com Lava-Olhos – CLO EXCLO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ANSI Z358.1; Instrução Técnica do Corpo de Bombeiros Militar estadual; NR-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Construção de mureta em bloco de concreto estrutural com espaços para comportas em torno da construção, para contenção de enchentes;</t>
+          <t>Chuveiro de emergência combinado com lava-olhos CLO EXCLO ou similar de equivalência técnica. Em laboratórios e áreas com risco químico. Conforme NR-15 e ANSI Z358.1.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>civil|073-servicos-externos-fechamentos-em-vidro-d</t>
+          <t>civil|073-chuveiro-eletrico-lorenzetti-maxducha-ul</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serviços externos - Fechamentos em vidro de segurança para o muro da fachada</t>
+          <t>Chuveiro Elétrico – Lorenzetti MaxDucha Ultra 5500W 220V</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410; NR-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fechamentos em vidro de segurança para o muro da fachada;</t>
+          <t>Chuveiro elétrico Lorenzetti MaxDucha Ultra 5500W 220V ou similar de equivalência técnica. Circuito elétrico exclusivo conforme NR-10 e NBR 5410.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>civil|074-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|074-chuveiro-para-pcd-lorenzetti-jet-control</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de estrutura metálica, fundação de concreto armado e cobertura em Ste</t>
+          <t>Chuveiro para PCD – Lorenzetti Jet Control Multitemperatura</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410; ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Construção de estrutura metálica, fundação de concreto armado e cobertura em Steel Deck para ampliação de área construída de salas de aula, incluindo impermeabilização da cobertura e da fundação. Fechamento da fachada em esquadrias de alumínio e vidro e peitoril em bloco cerâmico, revestido em cerâmica tipo tijolinho;</t>
+          <t>Chuveiro PCD Lorenzetti Jet Control ou similar de equivalência técnica com barra deslizante e mangueira flexível. Conforme NBR 9050:2020.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>civil|075-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|075-barras-de-apoio-deca-conforto-inox-60-70</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Acessórios para PCD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de esquadrias de alumínio, portas e janelas, nas salas de aula</t>
+          <t>Barras de Apoio Deca Conforto Inox – 60 / 70 / 80 cm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 9050:2020</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Instalação de esquadrias de alumínio, portas e janelas, nas salas de aula;</t>
+          <t>Barras de apoio Deca Conforto ou similar de equivalência técnica inox 60, 70 e 80 cm. Conforme NBR 9050:2020.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>civil|076-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>civil|076-valvula-de-duplo-acionamento-docol-class</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Louças e Metais</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de portas para rota de fuga e para acesso aos vestiários</t>
+          <t>Válvula de Duplo Acionamento – Docol Clássica Salvágua</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15097</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Instalação de portas para rota de fuga e para acesso aos vestiários;</t>
+          <t>Válvula de descarga duplo acionamento Docol Clássica Salvágua ou similar de equivalência técnica. Volume reduzido para urina, normal para fezes.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>civil|077-servicos-do-pavimento-terreo-quadra-poli</t>
+          <t>civil|077-espelho-cristal-incolor-50100-cm-4-mm-fi</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Acabamentos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Instalação de novo portão na fachada da quadra para acesso de plataforma de manu</t>
+          <t>Espelho Cristal Incolor 50×100 cm – 4 mm, Fita Dupla Face</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 7199</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Instalação de novo portão na fachada da quadra para acesso de plataforma de manutenção;</t>
+          <t>Espelho cristal incolor 50×100 cm, e=4 mm, fixação em fita dupla face sobre suporte MDF, sem moldura.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>civil|078-servicos-do-pavimento-terreo-quadra-poli</t>
+          <t>civil|078-alcapao-de-metal-para-drywall-5050-cm-br</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Acabamentos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Substituição das portas existentes conforme projeto</t>
+          <t>Alçapão de Metal para Drywall 50×50 cm – Branco</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t/>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Substituição das portas existentes conforme projeto;</t>
+          <t>Alçapão metálico com tampa 50×50 cm, cor branco, para embutir em forros e paredes de drywall.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>civil|079-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|079-pintura-de-paredes-internas-em-latex-acr</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Pinturas</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Instalação de esquadrias de alumínio, portas e janelas, nos novos ambientes</t>
+          <t>Pintura de Paredes Internas em Látex Acrílico – Suvinil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13245</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Instalação de esquadrias de alumínio, portas e janelas, nos novos ambientes;</t>
+          <t>Tinta látex acrílica Suvinil ou similar de equivalência técnica, 2 demãos, sobre selador e massa corrida PVA. Cores: branco fosco, algodão egípcio, preto fosco, cinza.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>civil|080-servicos-do-1-pavimento-area-de-saude-in</t>
+          <t>civil|080-pintura-de-fachada-em-acrilica-verde-aci</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12 - Esquadrias</t>
+          <t>Pinturas</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Instalação de esquadrias de alumínio, portas, janelas, lavatórios e ralos nos no</t>
+          <t>Pintura de Fachada em Acrílica – Verde Acinzentado Floresta Pantanal</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13245</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Instalação de esquadrias de alumínio, portas, janelas, lavatórios e ralos nos novos ambientes.</t>
+          <t>Tinta acrílica Suvinil Floresta Pantanal ou similar de equivalência técnica, 2 demãos, sobre selador externo. Remoção de eflorescências.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>civil|081-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|081-pintura-de-tetos-em-tinta-pva-branco</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>14 - Rodapés, Soleiras, Peitoris,Testeira, Bancadas e Prateleiras</t>
+          <t>Pinturas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Instalação das peças em granito como soleiras, peitoris, bancadas, louças e meta</t>
+          <t>Pintura de Tetos em Tinta PVA Branco</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13245</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Instalação das peças em granito como soleiras, peitoris, bancadas, louças e metais e acessórios sanitários, espelhos e demais itens listados em projetos, detalhes e planilha orçamentária;</t>
+          <t>Tinta PVA branco, 2 demãos, sobre superfície preparada. Lixamento entre demãos.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>civil|082-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|082-pintura-de-esquadrias-metalicas-esmalte-</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14 - Rodapés, Soleiras, Peitoris,Testeira, Bancadas e Prateleiras</t>
+          <t>Pinturas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços do 1° pavimento - Área de salas de aula - Instalação de bancadas de granito com cubas de inox nas salas de aula, conforme </t>
+          <t>Pintura de Esquadrias Metálicas – Esmalte Sherwin Williams RAL 7010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13245</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Instalação de bancadas de granito com cubas de inox nas salas de aula, conforme indicado em projeto;</t>
+          <t>Esmalte ecológico Sherwin Williams RAL 7010 ou similar de equivalência técnica, 2 demãos, sobre limpeza mecânica e fundo anticorrosivo (zarcão ou primer conforme projeto).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>civil|083-servicos-do-1-pavimento-area-de-salas-de</t>
+          <t>civil|083-pintura-de-arquibancada-em-tinta-acrilic</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14 - Rodapés, Soleiras, Peitoris,Testeira, Bancadas e Prateleiras</t>
+          <t>Pinturas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Construção de peitoril em alvenaria de bloco cerâmico, na área da varanda</t>
+          <t>Pintura de Arquibancada em Tinta Acrílica Cinza Médio</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13245</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Construção de peitoril em alvenaria de bloco cerâmico, na área da varanda.</t>
+          <t>Tinta acrílica cinza médio, 2 demãos, sobre selador e massa niveladora. Adição de novos degraus conforme CBMERJ.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>civil|084-servicos-do-1-pavimento-area-de-saude-in</t>
+          <t>civil|084-marcenaria-em-mdf-ultra-18-mm-com-hpl-e-</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14 - Rodapés, Soleiras, Peitoris,Testeira, Bancadas e Prateleiras</t>
+          <t>Marcenaria</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Instalação de bancadas de granito com cubas de inox nas salas indicadas em proje</t>
+          <t>Marcenaria em MDF Ultra 18 mm com HPL e Soft-Close</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14810-2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Instalação de bancadas de granito com cubas de inox nas salas indicadas em projeto;</t>
+          <t>Armários e bancadas em MDF Ultra 18 mm ou similar de equivalência técnica, HPL externo branco e laranja, dobradiças soft-close, corrediças telescópicas, pés reguláveis metálicos.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>civil|085-faz-parte-do-servico-da-contratada-a-ent</t>
+          <t>civil|085-limpeza-final-da-obra</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>17 - Diversos</t>
+          <t>Serviços Finais</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Faz parte do serviço da CONTRATADA: - A entrega deverá ocorrer em dois formatos: impresso e digital (</t>
+          <t>Limpeza Final da Obra</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>CONAMA Resolução 307/2002; NR-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>A entrega deverá ocorrer em dois formatos: impresso e digital (.MPP – Microsoft Project);</t>
+          <t>Limpeza fina completa ao final de todos os serviços. Remoção de entulhos, limpeza de pisos, paredes, esquadrias, vidros e equipamentos. Descarte conforme CONAMA 307.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>civil|086-faz-parte-do-servico-da-contratada-as-re</t>
+          <t>civil|086-as-built-em-plataforma-bim-e-acervo-foto</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>17 - Diversos</t>
+          <t>Serviços Finais</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Faz parte do serviço da CONTRATADA: - As reuniões ocorrerão periodicamente, com frequência mínima semanal</t>
+          <t>As-Built em Plataforma BIM e Acervo Fotográfico</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR ISO 19650-2; ABNT NBR 13532</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>As reuniões ocorrerão periodicamente, com frequência mínima semanal;</t>
+          <t>Elaboração de projeto as-built em plataforma BIM (formato IFC compatível com Revit/ArchiCAD) para todas as disciplinas, com registro das alterações ocorridas durante a obra. Acervo fotográfico georreferenciado por etapa. Entrega em repositório digital e em mídia física.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>civil|087-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|087-manual-do-usuario-e-de-manutencao-da-obr</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>17 - Diversos</t>
+          <t>Serviços Finais</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Proteção dos elementos e estruturas existentes no entorno da obra, edificações v</t>
+          <t>Manual do Usuário e de Manutenção da Obra</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14037</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Proteção dos elementos e estruturas existentes no entorno da obra, edificações vizinhas e outras, que possam ser afetados de alguma forma durante a execução dos serviços; Proteção da edificação preservada, principalmente quanto às suas características volumétricas, conforme projetos e planilha anexa;</t>
+          <t>Elaboração de Manual do Usuário contendo: especificação dos materiais aplicados, garantias dos sistemas instalados, recomendações de uso e manutenção preventiva, contatos dos fabricantes e prestadores de serviço. Conforme ABNT NBR 14037.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>civil|088-relacao-dos-principais-servicos-a-serem-</t>
+          <t>civil|088-testes-de-comissionamento-e-recebimento-</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17 - Diversos</t>
+          <t>Serviços Finais</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento de todos os materiais e mão de obra</t>
+          <t>Testes de Comissionamento e Recebimento de Sistemas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401; ABNT NBR 5410; ABNT NBR 13714</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fornecimento de todos os materiais e mão de obra;</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>civil|089-relacao-dos-principais-servicos-a-serem-</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Demolições conforme projeto específico, com o descarte adequado</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Demolições conforme projeto específico, com o descarte adequado;</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>civil|090-relacao-dos-principais-servicos-a-serem-</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e instalação da Sinalização de Emergência</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Fornecimento e instalação da Sinalização de Emergência;</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>civil|091-relacao-dos-principais-servicos-a-serem-</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Transporte horizontal e vertical dos equipamentos e insumos da obra</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Transporte horizontal e vertical dos equipamentos e insumos da obra;</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>civil|092-ambientes-em-reforma-estacionamentos-ace</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ambientes em reforma: Estacionamentos, acessos, área da escola, restaurante do c</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Ambientes em reforma: Estacionamentos, acessos, área da escola, restaurante do clube, áreas da saúde, áreas técnicas indicadas em projeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>civil|093-ambientes-parcialmente-no-escopo</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ambientes parcialmente no escopo:</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Ambientes parcialmente no escopo:.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>civil|094-ambientes-fora-do-escopo-clube-exceto-re</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ambientes fora do escopo: Clube (exceto restaurante e acessos vinculados), sanit</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Ambientes fora do escopo: Clube (exceto restaurante e acessos vinculados), sanitários da torre e sanitários coletivos da saúde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>civil|095-demolicoes-areas-externas-instalacoes-su</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Demolições - Áreas externas - Instalações subterrâneas e reservatórios de retardo</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Instalações subterrâneas e reservatórios de retardo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>civil|096-demolicoes-areas-externas-criacao-de-jar</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Demolições - Áreas externas - Criação de jardins “bacia” de contenção de chuva</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Criação de jardins “bacia” de contenção de chuva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>civil|097-servicos-externos-substituicao-dos-porto</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Serviços externos - Substituição dos portões de pedestres e portões de veículos motorizado</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Substituição dos portões de pedestres e portões de veículos motorizado;</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>civil|098-servicos-externos-construcao-de-rampas-a</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Serviços externos - Construção de rampas acessíveis</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Construção de rampas acessíveis;</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>civil|099-servicos-externos-construcao-de-guaritas</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Serviços externos - Construção de guaritas para acesso à escola e ao Sesi Lazer</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Construção de guaritas para acesso à escola e ao Sesi Lazer;</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>civil|100-servicos-externos-construcao-de-abrigo-p</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Serviços externos - Construção de abrigo para compressor de ar</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Construção de abrigo para compressor de ar;</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>civil|101-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de novos sanitários</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Construção de novos sanitários;</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>civil|102-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Refeitório/ Sala multiuso e restaurante</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Refeitório/ Sala multiuso e restaurante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>civil|103-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Desmontagem das salas de aula temporárias</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Desmontagem das salas de aula temporárias;</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>civil|104-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Reforma do restaurante e construção de novo ambiente para cantina</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Reforma do restaurante e construção de novo ambiente para cantina;</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>civil|105-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de sanitários PCD</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Construção de sanitários PCD;</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>civil|106-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de sala de atendimento</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Construção de sala de atendimento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>civil|107-servicos-do-pavimento-terreo-quadra-poli</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Instalação de novas traves e tabelas</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Instalação de novas traves e tabelas;</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>civil|108-servicos-do-pavimento-terreo-quadra-poli</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Reforma completa dos vestiários existentes, com construção de novos vestiários P</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Reforma completa dos vestiários existentes, com construção de novos vestiários PCD, banheiros e salas de serviço;</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>civil|109-servicos-do-1-pavimento-area-de-saude-co</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>17 - Diversos</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Construção sanitários individuais</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Construção sanitários individuais;</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>civil|110-servicos-externos-emissao-de-art-especif</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Serviços externos - Emissão de ART específica para construção de estrutura, inclusive com pintura an</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Emissão de ART específica para construção de estrutura, inclusive com pintura anti-chama, conforme documentos anexos atinentes ao assunto;</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>civil|111-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Pintura das paredes das salas de aula e nas circulações</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Pintura das paredes das salas de aula e nas circulações;</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>civil|112-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de revestimentos em mdf e pintural esmalte nas paredes internas, conf</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Instalação de revestimentos em mdf e pintural esmalte nas paredes internas, conforme indicado em projeto;</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>civil|113-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Pintura das paredes periféricas</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Pintura das paredes periféricas;</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>civil|114-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Pintura interna e instalação de bancadas e novas instalações</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Pintura interna e instalação de bancadas e novas instalações;</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>civil|115-servicos-do-1-pavimento-area-de-salas-de</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Instalação de revestimentos em mdf laminado ou pintura esmalte conforme projeto</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Instalação de revestimentos em mdf laminado ou pintura esmalte conforme projeto;</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>civil|116-servicos-do-1-pavimento-area-de-salas-de</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>18 - Pinturas</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Pintura das paredes dos novos ambientes e nas circulações</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Pintura das paredes dos novos ambientes e nas circulações;</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>civil|117-relacao-dos-principais-servicos-a-serem-</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>30 - SERVIÇOS FINAIS</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Elaboração do As Built em plataforma BIM e Manual do Usuário</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Elaboração do As Built em plataforma BIM e Manual do Usuário;</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>civil|118-relacao-dos-principais-servicos-a-serem-</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>30 - SERVIÇOS FINAIS</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Limpeza final permanente da obra</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Limpeza final permanente da obra.</t>
+          <t>Realização de testes de comissionamento e recebimento de todos os sistemas instalados: verificação de desempenho, ajustes e regulagens finais. Emissão de relatório técnico de aceitação por sistema, assinado por responsável técnico.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3676,21 +2450,13 @@
           <t>BANCO_ESPECIFICACOES - Instalações Elétricas</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3722,227 +2488,241 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eletrica|001-relacao-dos-principais-servicos-a-serem-</t>
+          <t>eletrica|001-infraestrutura-eletrica-provisoria-do-ca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução de forros e revestimentos de teto e luminárias conforme projetos e espe</t>
+          <t>Infraestrutura Elétrica Provisória do Canteiro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410; NR-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Execução de forros e revestimentos de teto e luminárias conforme projetos e especificações;</t>
+          <t>Execução da infraestrutura elétrica provisória do canteiro, incluindo iluminação aparente em canaleta PVC com condutores 2,5 mm², alimentadores em cabos HEPR 90°C 0,6/1 kV. Toda a instalação deve atender à NR-10 e NBR 5410.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eletrica|002-relacao-dos-principais-servicos-a-serem-</t>
+          <t>eletrica|002-iluminacao-aparente-provisoria-em-canale</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e Instalação da Iluminação de Emergência</t>
+          <t>Iluminação Aparente Provisória em Canaleta ou Eletrocalha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410; NR-10; NR-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fornecimento e Instalação da Iluminação de Emergência;</t>
+          <t>Instalação de circuitos de iluminação aparente provisória para ambientes em operação temporária durante a obra, com condutores em canaleta PVC ou eletrocalha, luminárias de sobrepor e interruptores. O circuito deve estar interligado ao quadro de distribuição provisório e atender à NR-10 e NBR 5410.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eletrica|003-demolicoes-pavimento-terreo-escola-insta</t>
+          <t>eletrica|003-infraestrutura-eletrica-de-baixa-tensao-</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>Instalações Elétricas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Demolições - Pavimento térreo – Escola - Instalações de rebaixo, luminárias e instalações de entreforro (substituição)</t>
+          <t>Infraestrutura Elétrica de Baixa Tensão – Remoção e Nova Instalação</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13534; ABNT NBR 13570; ABNT NBR 5410; NR-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Instalações de rebaixo, luminárias e instalações de entreforro (substituição).</t>
+          <t>Remoção de infraestrutura obsoleta e instalação de nova: eletrodutos aço zincado (internos), galvanizado a fogo (externos), PVC rígido preto (entreforro); eletrocalhas perfuradas; perfilados galvanizados. Alimentadores HEPR 90°C, terminais PVC 70°C. Valas 0,3 m (terminais) / 0,7 m (alimentadores).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eletrica|004-servicos-externos-substituicao-dos-poste</t>
+          <t>eletrica|004-quadros-de-distribuicao-bt-ip54-ral-7032</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>Instalações Elétricas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serviços externos - Substituição dos postes de iluminação</t>
+          <t>Quadros de Distribuição BT – IP54 RAL 7032</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR IEC 60439-1:2003; ABNT NBR 5410; NR-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Substituição dos postes de iluminação;</t>
+          <t>Painéis de distribuição IP54, caixa RAL 7032, placa RAL 2000, fecho lingueta triângulo. Disjuntores termomagnéticos, DR e DPS. Sinaleira LED vermelha. Porta-documentos A3.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eletrica|005-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>eletrica|005-autotransformador-trifasico-300-kva-220-</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>Instalações Elétricas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de refletores</t>
+          <t>Autotransformador Trifásico 300 kVA 220/380V a Seco IP23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5356; ABNT NBR 5410; NR-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Instalação de refletores;</t>
+          <t>Autotransformador trifásico a seco, 300 kVA, 220/380 V, IP23, alumínio, 105°C. Base antivibrante. Ref. Wise ou similar.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eletrica|006-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>eletrica|006-spda-com-captores-pdi-pevectron-3-s60-t-</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16 - Luminárias</t>
+          <t>SPDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Substituição do forro e iluminação</t>
+          <t>SPDA com Captores PDI Pevectron 3 S60 – ΔT=60 μs</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5419-1; NF C17-102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Substituição do forro e iluminação;</t>
+          <t>SPDA com captores PDI Pevectron 3 S60 ou similar de equivalência técnica, ΔT=60 μs, NF C17-102 e NBR 5419-1. Hastes copperweld 5/8"×2,4 m (3 por descida). Descidas em cabo nú 50 mm². Conexões com solda exotérmica.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eletrica|007-servicos-externos-construcao-de-telas-de</t>
+          <t>eletrica|007-sensores-de-presenca-360-e-alarmes-visua</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20 - Instalações elétricas</t>
+          <t>Instalações Elétricas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serviços externos - Construção de telas de fechamento para controle de acesso e para isolamento do g</t>
+          <t>Sensores de Presença 360° e Alarmes Visuais PCD MINI-CSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410; ABNT NBR 9050:2020; Instrução Técnica do Corpo de Bombeiros Militar estadual; NR-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Construção de telas de fechamento para controle de acesso e para isolamento do gerador;</t>
+          <t>Sensores de presença 360° bivolt, alcance Ø 7 m, para banheiros. Alarmes visuais PCD MINI-CSL ou similar de equivalência técnica: amarelo (sinal de aula) e vermelho (alarme de incêndio). Botoeiras a 40 cm do piso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eletrica|008-tomadas-de-piso-em-inox-escovado-150250-</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Instalações Elétricas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tomadas de Piso em Inox Escovado 150×250 mm – NBR 14136</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ABNT NBR 14136; ABNT NBR 5410; NR-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Caixa plástica de engenharia 150×250×60 mm, módulos tomada NBR 14136, suportes RJ45. Tampa basculante 190×190 mm inox escovado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BANCO_ESPECIFICACOES - Instalações Hidrossanitárias</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+          <t>BANCO_ESPECIFICACOES - Dados, Voz e CFTV</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3974,173 +2754,106 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hidrossanitaria|001-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>dados|001-infraestrutura-de-dados-provisoria-do-ca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21 - INSTALAÇÕES HIDRÁULICAS ÁGUA FRIA</t>
+          <t>Instalações Provisórias</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de bancadas e prateleiras de granito e chuveiro lava-olhos no laborat</t>
+          <t>Infraestrutura de Dados Provisória do Canteiro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14565; NBR 16415; TIA-568; TIA-569</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Instalação de bancadas e prateleiras de granito e chuveiro lava-olhos no laboratório de ciências;</t>
+          <t>Execução da infraestrutura de dados e telefonia provisória para o canteiro, atendendo às normas TIA-568, TIA-569, NBR 14565 e NBR 16415.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hidrossanitaria|002-relacao-dos-principais-servicos-a-serem-</t>
+          <t>dados|002-infraestrutura-seca-para-tv-projetor-e-d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22 - INSTALAÇÕES DE ESGOTO SANITÁRIO / ÁGUAS PLUVIAIS</t>
+          <t>Instalações Especiais</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e instalação de ETE</t>
+          <t>Infraestrutura Seca para TV, Projetor e Dados – Eletroduto Galvanizado DN 2"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 14565; ABNT NBR 16415; ABNT NBR 5410; TIA-568; TIA-569</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fornecimento e instalação de ETE;</t>
+          <t>Eletrodutos galvanizados DN 2" para HDMI e dados em salas. Tomadas RJ45 em canaletas de alumínio. Guia arame galvanizado #16. Atender TIA-568, TIA-569, NBR 14565, NBR 16415.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hidrossanitaria|003-servicos-externos-instalacao-de-estacao-</t>
+          <t>dados|003-sistema-de-controle-de-acesso-com-cftv-e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22 - INSTALAÇÕES DE ESGOTO SANITÁRIO / ÁGUAS PLUVIAIS</t>
+          <t>Instalações Especiais</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serviços externos - Instalação de Estação de tratamento de esgoto, incluindo projeto, aprovação no ó</t>
+          <t>Sistema de Controle de Acesso com CFTV e Sensor Eletromagnético de Porta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5410</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Instalação de Estação de tratamento de esgoto, incluindo projeto, aprovação no órgão responsável e obras civis necessárias para a sua instalação;</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>hidrossanitaria|004-servicos-externos-forracao-com-britas-de</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>22 - INSTALAÇÕES DE ESGOTO SANITÁRIO / ÁGUAS PLUVIAIS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Serviços externos - Forração com britas de bacias de biorretenção</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Forração com britas de bacias de biorretenção;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>hidrossanitaria|005-servicos-do-1-pavimento-servicos-das-laj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>22 - INSTALAÇÕES DE ESGOTO SANITÁRIO / ÁGUAS PLUVIAIS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Serviços das lajes de cobertura – pavimentos técnicos - Impermeabilização e drenagem da nova laje da escada</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Impermeabilização e drenagem da nova laje da escada;</t>
+          <t>CFTV IP, leitores de crachá, botões de emergência e sensores eletromagnéticos nas portas indicadas. Infraestrutura em eletrodutos galvanizados.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BANCO_ESPECIFICACOES - Dados, Voz e CFTV</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+          <t>BANCO_ESPECIFICACOES - Instalações Hidrossanitárias</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4172,92 +2885,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dados|001-faz-parte-do-servico-da-contratada-serao</t>
+          <t>hidrossanitaria|001-rede-de-agua-fria-em-pvc-soldavel-regist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23 - Instalações especiais</t>
+          <t>Instalações Hidráulicas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faz parte do serviço da CONTRATADA: - Serão abordados: a gestão do projeto, resolução de problemas, comunicação entre </t>
+          <t>Rede de Água Fria em PVC Soldável – Registros em Bronze</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 5626; ABNT NBR 5648; ABNT NBR 7195:1995</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Serão abordados: a gestão do projeto, resolução de problemas, comunicação entre as partes, atualização do cronograma físico-financeiro e demais assuntos pertinentes ao andamento contratual.</t>
+          <t>Tubulação PVC soldável marrom, NBR 5648. Registros gaveta bronze ASTM B62. Valas ≥40 cm. Teste de estanqueidade 2× pressão de trabalho por ≥24h. Identificação NBR 7195.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dados|002-servicos-do-pavimento-terreo-area-de-sal</t>
+          <t>hidrossanitaria|002-rede-de-esgoto-aguas-pluviais-e-drenagem</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23 - Instalações especiais</t>
+          <t>Instalações Sanitárias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de pontos de dados e voz para catracas de controle de acesso</t>
+          <t>Rede de Esgoto, Águas Pluviais e Drenagem de Ar Condicionado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 10844; ABNT NBR 5688; ABNT NBR 7362</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Instalação de pontos de dados e voz para catracas de controle de acesso;</t>
+          <t>Esgoto em PVC. Ralos sifonados giro fácil 185×170×75 mm, grelha inox. Caixas de inspeção anéis concreto Ø0,60 m + SIKA ou similar de equivalência técnica. Drenagem condensado AC em PVC 40 mm com isolamento elastomérico 10 mm.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BANCO_ESPECIFICACOES - Climatização, Mecânica e Elevadores</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+          <t>BANCO_ESPECIFICACOES - Instalações Mecânicas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4289,551 +2989,187 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>climatizacao|001-servicos-externos-construcao-de-deposito</t>
+          <t>mecanica|001-splits-inverter-cassete-piso-teto-hi-wal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24 - INSTALAÇÕES DE GASES</t>
+          <t>Climatização / AVAC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serviços externos - Construção de depósito de gás</t>
+          <t>Splits Inverter – Cassete / Piso-Teto / Hi-Wall</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401; ABNT NBR 5410</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Construção de depósito de gás;</t>
+          <t>Splits inverter de alta eficiência, tipos cassete, piso-teto e hi-wall, 220V monofásico. Tubulação de cobre foscoper com solda em nitrogênio, vácuo entre 300 e 500 microns, isolamento elastomérico 13 mm. Suportes antivibratórios para condensadoras.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>climatizacao|002-relacao-dos-principais-servicos-a-serem-</t>
+          <t>mecanica|002-sistema-vrf-condensadoras-e-evaporadoras</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
+          <t>Climatização / AVAC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Execução das instalações hidráulicas, instalações de esgoto, drenagem do ar-cond</t>
+          <t>Sistema VRF – Condensadoras e Evaporadoras R410A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401; ABNT NBR 5410</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Execução das instalações hidráulicas, instalações de esgoto, drenagem do ar-condicionado, instalações elétricas, luminárias, sistema de ar-condicionado, exaustão e ventilação mecânica, sistema de detecção, combate e extinção de incêndio e demais sistemas e equipamentos;</t>
+          <t>Sistema de refrigerante variável (VRF), com condensadoras em R410A e evaporadoras dos tipos cassete, piso-teto e hi-wall. Tubulação de cobre com bifurcações e soldagem em nitrogênio. Vácuo e ensaio de estanqueidade antes da carga de gás. Isolamento elastomérico 25 mm. Cabos de comunicação bus VRF. Suportes antivibratórios para condensadoras.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>climatizacao|003-relacao-dos-principais-servicos-a-serem-</t>
+          <t>mecanica|003-ventiladores-de-exaustao-sirocco-e-inlin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
+          <t>Climatização / AVAC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento de mão de obra para a desinstalação de splits existentes</t>
+          <t>Ventiladores de Exaustão – Sirocco e Inline</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401; ABNT NBR 5410</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fornecimento de mão de obra para a desinstalação de splits existentes;</t>
+          <t>Ventilador centrífugo tipo sirocco para exaustão geral, trifásico; ventiladores inline monofásicos para exaustão de sanitários e áreas técnicas. Instalação em dutos, ligação elétrica, suportes antivibratórios e balanceamento.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>climatizacao|004-relacao-dos-principais-servicos-a-serem-</t>
+          <t>mecanica|004-gabinetes-de-renovacao-de-ar-com-filtrag</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
+          <t>Climatização / AVAC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e instalação de sistemas de climatização e renovação de ar</t>
+          <t>Gabinetes de Renovação de Ar com Filtragem G4 e Quadro de Comando</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401; ABNT NBR 5410</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fornecimento e instalação de sistemas de climatização e renovação de ar;</t>
+          <t>Gabinetes de ventilação para renovação de ar com filtro de classe G4, motor conforme projeto, quadro de comando dedicado. Instalação inclui dutos de tomada de ar externo, registros de ar, grelhas de insuflamento e ligação elétrica.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>climatizacao|005-academia-substituicao-do-sistema-de-ar-c</t>
+          <t>mecanica|005-dutos-tdc-em-aco-galvanizado-com-grelhas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
+          <t>Climatização / AVAC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Academia: substituição do sistema de ar-condicionado e dos rebaixos afetados</t>
+          <t>Dutos TDC em Aço Galvanizado com Grelhas em Alumínio e Dampers de Controle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 16401</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Academia: substituição do sistema de ar-condicionado e dos rebaixos afetados.</t>
+          <t>Dutos TDC em aço galvanizado conforme NBR 16401. Grelhas de simples deflexão em alumínio anodizado. Dampers de controle de vazão manual e sobrepressão. Visitas estanques a cada 5 m. Anticorrosão externa nas seções expostas.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>climatizacao|006-cozinha-do-restaurante-substituicao-do-s</t>
+          <t>mecanica|006-elevador-eletrico-sem-casa-de-maquinas-4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
+          <t>Elevadores</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cozinha do restaurante: substituição do sistema de exaustão</t>
+          <t>Elevador Elétrico sem Casa de Máquinas – 400 kg – ABNT NBR 12892</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 12892:2009; ABNT NBR NM 207:1999; ABNT NBR NM 267:2001; ABNT NBR NM 213-2:1999; ABNT NBR 9050:2020; NR-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cozinha do restaurante: substituição do sistema de exaustão.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>climatizacao|007-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de dados e voz conforme indicados no projeto;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>climatizacao|008-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Manutenção de esquadria de alumínio existente com substituição das vedações, rev</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Manutenção de esquadria de alumínio existente com substituição das vedações, revisão do sistema de abertura recomposição dos vidros de ar-condicionado e quebrados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>climatizacao|009-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Construção de salas de aula temporárias em divisória de gesso acartonado e forro</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Construção de salas de aula temporárias em divisória de gesso acartonado e forro em isopor, com aproveitamento dos aparelhos de ar-condicionado da unidade;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>climatizacao|010-servicos-do-pavimento-terreo-area-de-sal</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Área de salas de aula e refeitório - Substituição do sistema de exaustão do restaurante</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Substituição do sistema de exaustão do restaurante;</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>climatizacao|011-servicos-do-pavimento-terreo-quadra-poli</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Serviços do pavimento térreo - Quadra Poliesportiva - Construção de salas de aula temporárias em divisória de gesso acartonado e forro</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Construção de salas de aula temporárias em divisória de gesso acartonado e forro de isopor, com aproveitamento dos aparelhos de ar-condicionado da unidade.;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>climatizacao|012-servicos-do-1-pavimento-area-de-salas-de</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de dados e voz nos novos ambientes e nas circulações;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>climatizacao|013-servicos-do-1-pavimento-area-de-salas-de</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de salas de aula - Substituição das esquadrias da fachada e recomposição dos vidros de ar-condicion</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Substituição das esquadrias da fachada e recomposição dos vidros de ar-condicionado e quebrados;</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>climatizacao|014-servicos-do-1-pavimento-area-de-saude-in</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Área de saúde - Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Instalação de rebaixo, nova iluminação, climatização, instalações elétricas e de dados e voz nos novos ambientes;</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>climatizacao|015-servicos-do-1-pavimento-servicos-das-laj</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Serviços das lajes de cobertura – pavimentos técnicos - Construção de bases de concreto para as condensadoras de ar-condicionado</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Construção de bases de concreto para as condensadoras de ar-condicionado;</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>climatizacao|016-servicos-do-1-pavimento-servicos-das-laj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>25 - INSTALAÇÕES MECÂNICAS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Serviços do 1° pavimento - Serviços das lajes de cobertura – pavimentos técnicos - Construção de estrutura metálica e piso em gradex para apoio de condensadoras de</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Construção de estrutura metálica e piso em gradex para apoio de condensadoras de ar-condicionado, com impermeabilização e drenagem da laje sob o trecho.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>climatizacao|017-demolicoes-areas-externas-fundacoes-das-</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>26 - ELEVADOR</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Demolições - Áreas externas - Fundações das novas guaritas, da caixa de elevador, da nova escada de emergência</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fundações das novas guaritas, da caixa de elevador, da nova escada de emergência e da cobertura das catracas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>climatizacao|018-servicos-externos-construcao-de-estrutur</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>26 - ELEVADOR</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Serviços externos - Construção de estrutura metálica, com fundação em concreto e laje em Steel Deck </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Construção de estrutura metálica, com fundação em concreto e laje em Steel Deck para poço do elevador e patamar de acesso ao 1°andar incluindo laje de cobertura. Fechamento em alvenaria de bloco cerâmico na vertical na divisa do ginásio com a escada e bloco cerâmico horizontal na caixa de corrida do elevador;</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>climatizacao|019-servicos-externos-instalacao-de-elevador</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>26 - ELEVADOR</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Serviços externos - Instalação de elevador de 2 paradas, atendendo às normas de instalações mecânica</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Instalação de elevador de 2 paradas, atendendo às normas de instalações mecânicas e a NR 9050 atual e com apresentação de certificado de funcionamento. A CONTRATADA será responsável pelo fornecimento do contrato de manutenção dos elevadores pelo período necessário para viabilidade da obtenção da documentação e autorização de funcionamento.</t>
+          <t>Elevador elétrico sem casa de máquinas, 400 kg, 5 passageiros, 21 m/min, acionamento VVVF. Cabine inox AISI 304 escovado, 0,90×1,30×2,00 m. Portas automáticas abertura central. Vão livre 80×200 cm. Sinalização sonora e visual de andares. Painel com Braille e números em relevo. Limitador de sobrecarga. Telefone de emergência na cabine. Certificado de funcionamento e ART de instalação.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BANCO_ESPECIFICACOES - PPCI - Prevenção e Combate a Incêndio</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+          <t>BANCO_ESPECIFICACOES - PPCI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Base inicial extraída do roteiro modelo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4865,220 +3201,458 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ppci|001-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|001-extintores-de-incendio-ap-co2-e-pqs</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Emissão de ARTs específicas para obra, instalação de equipamentos mecânicos, con</t>
+          <t>Extintores de Incêndio – AP, CO2 e PQS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 12693; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emissão de ARTs específicas para obra, instalação de equipamentos mecânicos, construção de estrutura, inclusive com pintura anti-chama e instalações de prevenção e combate à incêndio, conforme documentos anexos atinentes ao assunto;</t>
+          <t>Extintores AP (circulação), CO2 (equipamentos elétricos) e PQS (subestação e GLP). INMETRO. Área máxima: 150 m².</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ppci|002-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|002-sinalizacao-de-emergencia-em-pvc-expandi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e Instalação e recarga de Extintores</t>
+          <t>Sinalização de Emergência em PVC Expandido 3 mm – Serigrafia – Garantia 36 meses</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13434; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fornecimento e Instalação e recarga de Extintores;</t>
+          <t>Sinalização completa em PVC expandido 3 mm com serigrafia, garantia mínima 36 meses. Rotas de fuga, extintores, hidrantes, saídas. Toda nova.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ppci|003-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|003-iluminacao-de-emergencia-blocos-autonomo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Adequação da rede de Hidrantes em rede pressurizada</t>
+          <t>Iluminação de Emergência – Blocos Autônomos IP23, 2h</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 10898; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adequação da rede de Hidrantes em rede pressurizada;</t>
+          <t>Blocos autônomos IP23, autonomia ≥2h. Mínimo 5 lux em escadas e 3 lux em corredores. Comutação ≤12 segundos. Conforme NBR 10898.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ppci|004-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|004-sistema-de-pressurizacao-de-hidrantes-el</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e Instalação do Sistema de Alarme de Incêndio</t>
+          <t>Sistema de Pressurização de Hidrantes – Eletrobombas Principal e Reserva</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13714; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fornecimento e Instalação do Sistema de Alarme de Incêndio;</t>
+          <t>2 eletrobombas (principal + reserva), 44,5 mca, 12 m³/h. Manômetro RECORD ou similar de equivalência técnica, pressostato PENN 47 AA-9004 ou similar de equivalência técnica, tanque hidropneumático 12 L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ppci|005-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|005-lge-afff-6-e-carreta-proporcionadora</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Fornecimento e instalação da carreta de LGE</t>
+          <t>LGE AFFF 6% e Carreta Proporcionadora</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 15511; Instrução Técnica do Corpo de Bombeiros Militar estadual; NFPA 11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fornecimento e instalação da carreta de LGE.</t>
+          <t>LGE AFFF 6% conforme NFPA 11 e ABNT NBR 15511. Carreta inox ou PEAD. Treinamento. FISPQ e certificados.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ppci|006-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|006-sistema-fixo-de-extincao-por-co2-dutos-d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Manutenção na casa de máquinas de incêndio</t>
+          <t>Sistema Fixo de Extinção por CO2 – Dutos de Cozinha</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 12232; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manutenção na casa de máquinas de incêndio;</t>
+          <t>Cilindros Mannesmann SAE-1541 ou similar de equivalência técnica, detectores fusível 144°C, dampers corta-fogo. Acionamento automático e manual. Inundação total ≥60 s.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ppci|007-relacao-dos-principais-servicos-a-serem-</t>
+          <t>ppci|007-canalizacao-preventiva-em-ferro-galvaniz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Relação dos principais serviços a serem executados: - Principais serviços gerais - Solicitar e tramitar a instalação do Hidrante Urbano</t>
+          <t>Canalização Preventiva em Ferro Galvanizado Ø 65 mm – 180 kgf/cm²</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13714; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Solicitar e tramitar a instalação do Hidrante Urbano;</t>
+          <t>Tubulação FG Ø 65 mm, 180 kgf/cm², pintada de vermelho (Ypiranga nº 217 ou similar de equivalência técnica). Braçadeiras econômicas, chumbadores CB 3/8", espaçamento médio 3,00 m.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ppci|008-servicos-externos-instalacoes-de-proteca</t>
+          <t>ppci|008-hidrantes-internos-caixas-754517-cm-com-</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27 - INSTALAÇÕES DE INCÊNDIO</t>
+          <t>PPCI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serviços externos - Instalações de proteção contra incêndio e sinalização de segurança</t>
+          <t>Hidrantes Internos – Caixas 75×45×17 cm com Mangueiras Tipo II</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ABNT NBR 15575; ABNT NBR 16280</t>
+          <t>ABNT NBR 13714; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Instalações de proteção contra incêndio e sinalização de segurança;</t>
+          <t>Caixas 75×45×17 cm. Registro globo angular 2½"×45°, 2 lances mangueira 1½" tipo II com 15 m, adaptador Storz 2½", esguichos jato regulável. Boca a 1,20 m do piso. Alcance máximo 30 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ppci|009-hidrante-de-recalque-registro-de-passeio</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PPCI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hidrante de Recalque – Registro de Passeio / Fachada</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ABNT NBR 13714; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Caixa FF 40×30 cm ('INCÊNDIO' na tampa), registro globo angular 2½"×45°. Profundidade 40 cm. Rebordo ≥15 cm do solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ppci|010-sistema-de-alarme-de-incendio-central-2-</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PPCI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sistema de Alarme de Incêndio – Central 2 Laços Classe B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ABNT NBR 17240; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Central 2 laços Classe B. Acionadores manuais PVC vermelho, sirenes audiovisuais 100 dB / 20 LEDs. Cabos PP 1,0 e 1,5 mm². Protocolo aberto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ppci|011-detectores-de-fumaca-e-calor-enderecavei</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PPCI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Detectores de Fumaça e Calor Endereçáveis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ABNT NBR 17240; ABNT NBR 9441; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Detectores óptico-eletrônicos de fumaça e calor endereçáveis, interligados à central de alarme. Instalados em tetos conforme espaçamento máximo de norma. Teste funcional individual após comissionamento. Base de fixação universal para substituição sem ferramentas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ppci|012-iluminacao-de-emergencia-sistema-central</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PPCI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Iluminação de Emergência – Sistema Centralizado com Bateria Supervisada</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ABNT NBR 10898; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sistema centralizado de iluminação de emergência com bateria supervisionada (VRLA), autonomia ≥3h, para edificações de maior porte. Central com supervisão de cada luminária. Mínimo 5 lux em escadas e rotas de fuga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ppci|013-plano-de-emergencia-da-edificacao-e-laud</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PPCI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Plano de Emergência da Edificação e Laudo de Materiais</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ABNT NBR 15219; Instrução Técnica do Corpo de Bombeiros Militar estadual</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Elaboração do Plano de Emergência da Edificação conforme Instrução Técnica estadual, incluindo: organização de brigada, rotas de fuga, pontos de encontro, responsáveis e procedimentos. Laudo de materiais construtivos quanto à reação ao fogo quando exigido.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BANCO_ESPECIFICACOES - Paisagismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gerado a partir de memorial_servicos.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHAVE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TIPO_SERVICO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NOME_SERVICO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NORMAS_ABNT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TEXTO_TECNICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>paisagismo|001-forracoes-e-gramados-em-areas-externas</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Paisagismo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Forrações e Gramados em Áreas Externas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ABNT NBR 9959</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Plantio de forrações (grama esmeralda, grama bermuda ou espécie conforme projeto) em áreas externas. Preparo do solo com topsoil e fertilizante. Irrigação pós-plantio. Grama em leiva ou sementes conforme especificação de projeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>paisagismo|002-plantio-de-arvores-ornamentais-e-arbusto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Paisagismo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Plantio de Árvores Ornamentais e Arbustos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ABNT NBR 9959</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fornecimento e plantio de árvores ornamentais e arbustos conforme projeto paisagístico. Cova conforme porte, adubação de fundação, tutoramento e irrigação inicial. Espécies preferencialmente nativas ou adaptadas ao clima local.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>